--- a/data/trans_camb/P05A_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P05A_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-26,21</t>
+          <t>-26,38</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-31,47</t>
+          <t>-31,03</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-28,87</t>
+          <t>-28,7</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 10,85</t>
+          <t>0,26; 10,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 9,39</t>
+          <t>-0,95; 9,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,67; -22,04</t>
+          <t>-30,5; -22,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 5,76</t>
+          <t>-4,86; 5,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 6,47</t>
+          <t>-4,08; 6,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,17; -27,14</t>
+          <t>-34,99; -27,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 7,0</t>
+          <t>-0,62; 6,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 6,41</t>
+          <t>-0,66; 6,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-31,45; -25,89</t>
+          <t>-31,75; -25,85</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-78,33%</t>
+          <t>-78,82%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-83,97%</t>
+          <t>-82,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-81,42%</t>
+          <t>-80,95%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 34,78</t>
+          <t>0,72; 32,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 29,79</t>
+          <t>-2,59; 30,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-85,11; -70,05</t>
+          <t>-84,88; -71,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 16,16</t>
+          <t>-12,29; 15,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 19,13</t>
+          <t>-9,92; 18,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-88,05; -78,22</t>
+          <t>-86,41; -77,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 20,92</t>
+          <t>-1,66; 19,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 19,03</t>
+          <t>-1,8; 20,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-85,06; -76,93</t>
+          <t>-84,72; -76,79</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-19,94</t>
+          <t>-18,01</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-22,05</t>
+          <t>-22,11</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-21,25</t>
+          <t>-20,06</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 6,18</t>
+          <t>-2,43; 6,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 4,95</t>
+          <t>-3,87; 4,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,38; -15,6</t>
+          <t>-21,95; -14,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 0,17</t>
+          <t>-8,39; 0,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,42; -2,26</t>
+          <t>-10,18; -1,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,58; -18,51</t>
+          <t>-25,77; -18,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 1,97</t>
+          <t>-4,37; 1,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 0,39</t>
+          <t>-5,5; 0,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-25,7; -18,18</t>
+          <t>-22,74; -17,17</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-67,13%</t>
+          <t>-60,66%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-60,73%</t>
+          <t>-60,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-64,37%</t>
+          <t>-60,77%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 22,58</t>
+          <t>-7,83; 22,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 18,43</t>
+          <t>-11,89; 17,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-84,65; -54,15</t>
+          <t>-68,4; -51,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,43; 0,55</t>
+          <t>-21,84; 0,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,12; -6,36</t>
+          <t>-26,31; -5,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,99; -53,9</t>
+          <t>-66,57; -54,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 6,11</t>
+          <t>-12,5; 5,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 1,41</t>
+          <t>-15,76; 1,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-77,14; -57,36</t>
+          <t>-65,64; -54,85</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-9,65</t>
+          <t>-9,16</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,86</t>
+          <t>-8,3</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>-8,73</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,98; 15,62</t>
+          <t>5,57; 15,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,55; 16,08</t>
+          <t>6,08; 16,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,72; -4,54</t>
+          <t>-14,25; -4,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,76; 17,85</t>
+          <t>7,46; 17,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 16,82</t>
+          <t>7,06; 17,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 40,82</t>
+          <t>-12,25; -3,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,79; 15,12</t>
+          <t>8,09; 15,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,03; 14,73</t>
+          <t>8,1; 15,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 27,26</t>
+          <t>-11,53; -5,18</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-34,38%</t>
+          <t>-32,62%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>-30,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>-31,34%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,27; 61,23</t>
+          <t>17,66; 61,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,22; 65,7</t>
+          <t>19,57; 63,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-48,82; -17,87</t>
+          <t>-45,89; -17,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26,2; 72,98</t>
+          <t>24,81; 68,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,16; 68,49</t>
+          <t>22,79; 67,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,05; 165,88</t>
+          <t>-40,55; -14,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,9; 58,0</t>
+          <t>27,51; 59,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,93; 56,21</t>
+          <t>27,09; 58,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-35,93; 107,84</t>
+          <t>-39,31; -20,56</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>6,06</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,69</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>3,5</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,31; 26,65</t>
+          <t>17,96; 26,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,92; 14,75</t>
+          <t>6,11; 14,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 9,3</t>
+          <t>1,41; 10,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,99; 17,7</t>
+          <t>8,64; 17,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 8,95</t>
+          <t>-0,2; 8,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 1,94</t>
+          <t>-2,74; 5,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,3; 20,95</t>
+          <t>14,7; 20,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,95; 10,17</t>
+          <t>4,24; 10,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 4,23</t>
+          <t>0,67; 6,36</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-7,67%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>61,67; 104,58</t>
+          <t>59,97; 104,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,01; 57,1</t>
+          <t>20,14; 55,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,74; 35,94</t>
+          <t>4,57; 39,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24,01; 53,54</t>
+          <t>23,26; 53,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,08; 27,7</t>
+          <t>-0,47; 25,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 5,5</t>
+          <t>-7,29; 16,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,97; 70,87</t>
+          <t>44,47; 69,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,74; 33,97</t>
+          <t>13,22; 33,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 14,32</t>
+          <t>2,07; 21,42</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-12,34</t>
+          <t>-10,97</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-10,83</t>
+          <t>-14,03</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-11,51</t>
+          <t>-12,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,9; 12,28</t>
+          <t>7,9; 12,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,6</t>
+          <t>4,22; 8,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-16,29; -9,92</t>
+          <t>-13,09; -8,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,94; 7,61</t>
+          <t>3,05; 7,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,41</t>
+          <t>0,02; 4,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 4,42</t>
+          <t>-16,05; -11,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,19; 9,44</t>
+          <t>6,15; 9,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,79</t>
+          <t>2,57; 5,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-14,58; -2,81</t>
+          <t>-13,91; -11,09</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-41,79%</t>
+          <t>-37,16%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-31,46%</t>
+          <t>-40,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-35,96%</t>
+          <t>-39,09%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>25,96; 43,73</t>
+          <t>26,31; 43,88</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>13,43; 30,16</t>
+          <t>13,65; 30,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,14; -34,47</t>
+          <t>-43,31; -31,31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8,2; 22,51</t>
+          <t>8,59; 23,08</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 13,2</t>
+          <t>0,11; 14,36</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-45,73; 13,33</t>
+          <t>-45,13; -36,02</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,72; 29,92</t>
+          <t>18,77; 30,56</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8,15; 18,54</t>
+          <t>7,74; 18,72</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-45,53; -8,88</t>
+          <t>-42,38; -35,29</t>
         </is>
       </c>
     </row>
